--- a/model_results_diabetes.xlsx
+++ b/model_results_diabetes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3269,6 +3269,1112 @@
         <v>8.602929272067815</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G76" t="n">
+        <v>83</v>
+      </c>
+      <c r="H76" t="n">
+        <v>16</v>
+      </c>
+      <c r="I76" t="n">
+        <v>20</v>
+      </c>
+      <c r="J76" t="n">
+        <v>35</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.767119818739171</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.708249734136831</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.5679955703211517</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.6293664285993052</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1.931522130966187</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>99</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>55</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.04990005493164062</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>99</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>55</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.04992485046386719</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.6753246753246753</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G82" t="n">
+        <v>99</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>50</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.6645425700687466</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.5513702963702964</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.2348484848484849</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.3276751946607342</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.05079913139343262</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.5977011494252874</v>
+      </c>
+      <c r="G84" t="n">
+        <v>93</v>
+      </c>
+      <c r="H84" t="n">
+        <v>6</v>
+      </c>
+      <c r="I84" t="n">
+        <v>29</v>
+      </c>
+      <c r="J84" t="n">
+        <v>26</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>10</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.7152035959809624</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.6583997873471558</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.3854978354978356</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.4824891774891774</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.03950691223144531</v>
+      </c>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>30</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="G86" t="n">
+        <v>83</v>
+      </c>
+      <c r="H86" t="n">
+        <v>16</v>
+      </c>
+      <c r="I86" t="n">
+        <v>21</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>30</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.7607086197778953</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.6931432748538012</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.5640692640692639</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.6200182368603422</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1001591682434082</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>50</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="G88" t="n">
+        <v>83</v>
+      </c>
+      <c r="H88" t="n">
+        <v>16</v>
+      </c>
+      <c r="I88" t="n">
+        <v>21</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>50</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.7541248016922263</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.6864880952380952</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.554112554112554</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.6109334546497577</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>10</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.05010366439819336</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>100</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G90" t="n">
+        <v>81</v>
+      </c>
+      <c r="H90" t="n">
+        <v>18</v>
+      </c>
+      <c r="I90" t="n">
+        <v>20</v>
+      </c>
+      <c r="J90" t="n">
+        <v>35</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>100</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.7686144896879956</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.7060631860399662</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.5764069264069264</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.6314643523565218</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>10</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.04001784324645996</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="G92" t="n">
+        <v>78</v>
+      </c>
+      <c r="H92" t="n">
+        <v>21</v>
+      </c>
+      <c r="I92" t="n">
+        <v>23</v>
+      </c>
+      <c r="J92" t="n">
+        <v>32</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G93" t="n">
+        <v>83</v>
+      </c>
+      <c r="H93" t="n">
+        <v>16</v>
+      </c>
+      <c r="I93" t="n">
+        <v>20</v>
+      </c>
+      <c r="J93" t="n">
+        <v>35</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G94" t="n">
+        <v>83</v>
+      </c>
+      <c r="H94" t="n">
+        <v>16</v>
+      </c>
+      <c r="I94" t="n">
+        <v>20</v>
+      </c>
+      <c r="J94" t="n">
+        <v>35</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>10</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G95" t="n">
+        <v>83</v>
+      </c>
+      <c r="H95" t="n">
+        <v>16</v>
+      </c>
+      <c r="I95" t="n">
+        <v>20</v>
+      </c>
+      <c r="J95" t="n">
+        <v>35</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>30</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G96" t="n">
+        <v>83</v>
+      </c>
+      <c r="H96" t="n">
+        <v>16</v>
+      </c>
+      <c r="I96" t="n">
+        <v>20</v>
+      </c>
+      <c r="J96" t="n">
+        <v>35</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>50</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G97" t="n">
+        <v>83</v>
+      </c>
+      <c r="H97" t="n">
+        <v>16</v>
+      </c>
+      <c r="I97" t="n">
+        <v>20</v>
+      </c>
+      <c r="J97" t="n">
+        <v>35</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>100</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="G98" t="n">
+        <v>83</v>
+      </c>
+      <c r="H98" t="n">
+        <v>16</v>
+      </c>
+      <c r="I98" t="n">
+        <v>20</v>
+      </c>
+      <c r="J98" t="n">
+        <v>35</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="G99" t="n">
+        <v>48</v>
+      </c>
+      <c r="H99" t="n">
+        <v>51</v>
+      </c>
+      <c r="I99" t="n">
+        <v>23</v>
+      </c>
+      <c r="J99" t="n">
+        <v>32</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>0.003227949142456055</v>
+      </c>
+      <c r="M99" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.5354330708661418</v>
+      </c>
+      <c r="G100" t="n">
+        <v>61</v>
+      </c>
+      <c r="H100" t="n">
+        <v>38</v>
+      </c>
+      <c r="I100" t="n">
+        <v>21</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>0.001644134521484375</v>
+      </c>
+      <c r="M100" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.7402597402597403</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="G101" t="n">
+        <v>77</v>
+      </c>
+      <c r="H101" t="n">
+        <v>22</v>
+      </c>
+      <c r="I101" t="n">
+        <v>18</v>
+      </c>
+      <c r="J101" t="n">
+        <v>37</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>0.001262664794921875</v>
+      </c>
+      <c r="M101" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>10</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G102" t="n">
+        <v>81</v>
+      </c>
+      <c r="H102" t="n">
+        <v>18</v>
+      </c>
+      <c r="I102" t="n">
+        <v>20</v>
+      </c>
+      <c r="J102" t="n">
+        <v>35</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>0.001194000244140625</v>
+      </c>
+      <c r="M102" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>30</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G103" t="n">
+        <v>81</v>
+      </c>
+      <c r="H103" t="n">
+        <v>18</v>
+      </c>
+      <c r="I103" t="n">
+        <v>20</v>
+      </c>
+      <c r="J103" t="n">
+        <v>35</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="n">
+        <v>0.001145839691162109</v>
+      </c>
+      <c r="M103" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>50</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G104" t="n">
+        <v>81</v>
+      </c>
+      <c r="H104" t="n">
+        <v>18</v>
+      </c>
+      <c r="I104" t="n">
+        <v>20</v>
+      </c>
+      <c r="J104" t="n">
+        <v>35</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>0.001049041748046875</v>
+      </c>
+      <c r="M104" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>100</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="G105" t="n">
+        <v>82</v>
+      </c>
+      <c r="H105" t="n">
+        <v>17</v>
+      </c>
+      <c r="I105" t="n">
+        <v>20</v>
+      </c>
+      <c r="J105" t="n">
+        <v>35</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>0.0008018016815185547</v>
+      </c>
+      <c r="M105" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
